--- a/AAII_Financials/Yearly/BOXL_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BOXL_YR_FIN.xlsx
@@ -1012,7 +1012,7 @@
         <v>200</v>
       </c>
       <c r="E14" s="3">
-        <v>900</v>
+        <v>13200</v>
       </c>
       <c r="F14" s="3">
         <v>26800</v>
@@ -1063,7 +1063,7 @@
         <v>10300</v>
       </c>
       <c r="E15" s="3">
-        <v>20500</v>
+        <v>8200</v>
       </c>
       <c r="F15" s="3">
         <v>8900</v>
@@ -1132,7 +1132,7 @@
         <v>125400</v>
       </c>
       <c r="E17" s="3">
-        <v>154400</v>
+        <v>142100</v>
       </c>
       <c r="F17" s="3">
         <v>176200</v>
@@ -1183,7 +1183,7 @@
         <v>-16200</v>
       </c>
       <c r="E18" s="3">
-        <v>-18500</v>
+        <v>-6200</v>
       </c>
       <c r="F18" s="3">
         <v>500</v>
